--- a/data_mock/Area_3_Validacion_Informes.xlsx
+++ b/data_mock/Area_3_Validacion_Informes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>pH</t>
+          <t>Turbidez</t>
         </is>
       </c>
       <c r="C2" t="b">
@@ -456,7 +456,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Metales_Pesados</t>
+          <t>pH</t>
         </is>
       </c>
       <c r="C3" t="b">
@@ -466,12 +466,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M-001</t>
+          <t>M-004</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Microbiologia</t>
+          <t>Metales_Pesados</t>
         </is>
       </c>
       <c r="C4" t="b">
@@ -481,7 +481,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M-002</t>
+          <t>M-004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -496,12 +496,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M-002</t>
+          <t>M-005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Metales_Pesados</t>
+          <t>Nitratos</t>
         </is>
       </c>
       <c r="C6" t="b">
@@ -511,12 +511,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M-003</t>
+          <t>M-005</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>pH</t>
+          <t>Plaguicidas</t>
         </is>
       </c>
       <c r="C7" t="b">
@@ -535,6 +535,1236 @@
         </is>
       </c>
       <c r="C8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>M-006</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dureza_Total</t>
+        </is>
+      </c>
+      <c r="C9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>M-006</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Nitratos</t>
+        </is>
+      </c>
+      <c r="C10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>M-006</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Plaguicidas</t>
+        </is>
+      </c>
+      <c r="C11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>M-007</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dureza_Total</t>
+        </is>
+      </c>
+      <c r="C12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>M-007</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Metales_Pesados</t>
+        </is>
+      </c>
+      <c r="C13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>M-007</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Solidos_Disueltos</t>
+        </is>
+      </c>
+      <c r="C14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>M-007</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Turbidez</t>
+        </is>
+      </c>
+      <c r="C15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>M-007</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="C16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>M-008</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Cloro_Residual</t>
+        </is>
+      </c>
+      <c r="C17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>M-008</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Conductividad</t>
+        </is>
+      </c>
+      <c r="C18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>M-008</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Metales_Pesados</t>
+        </is>
+      </c>
+      <c r="C19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>M-008</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Microbiologia</t>
+        </is>
+      </c>
+      <c r="C20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>M-008</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Turbidez</t>
+        </is>
+      </c>
+      <c r="C21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>M-012</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Nitratos</t>
+        </is>
+      </c>
+      <c r="C22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>M-012</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Turbidez</t>
+        </is>
+      </c>
+      <c r="C23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>M-013</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Metales_Pesados</t>
+        </is>
+      </c>
+      <c r="C24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>M-013</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Plaguicidas</t>
+        </is>
+      </c>
+      <c r="C25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>M-013</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Solidos_Disueltos</t>
+        </is>
+      </c>
+      <c r="C26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>M-013</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="C27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>M-014</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Metales_Pesados</t>
+        </is>
+      </c>
+      <c r="C28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>M-014</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Plaguicidas</t>
+        </is>
+      </c>
+      <c r="C29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>M-014</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Turbidez</t>
+        </is>
+      </c>
+      <c r="C30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>M-015</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Dureza_Total</t>
+        </is>
+      </c>
+      <c r="C31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>M-015</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Turbidez</t>
+        </is>
+      </c>
+      <c r="C32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>M-016</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Conductividad</t>
+        </is>
+      </c>
+      <c r="C33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>M-016</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Metales_Pesados</t>
+        </is>
+      </c>
+      <c r="C34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>M-016</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Microbiologia</t>
+        </is>
+      </c>
+      <c r="C35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>M-016</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Nitratos</t>
+        </is>
+      </c>
+      <c r="C36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>M-016</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Solidos_Disueltos</t>
+        </is>
+      </c>
+      <c r="C37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>M-018</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Conductividad</t>
+        </is>
+      </c>
+      <c r="C38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>M-018</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Dureza_Total</t>
+        </is>
+      </c>
+      <c r="C39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>M-018</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Microbiologia</t>
+        </is>
+      </c>
+      <c r="C40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>M-018</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Plaguicidas</t>
+        </is>
+      </c>
+      <c r="C41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>M-018</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Turbidez</t>
+        </is>
+      </c>
+      <c r="C42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>M-019</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Plaguicidas</t>
+        </is>
+      </c>
+      <c r="C43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>M-019</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="C44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>M-020</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Cloro_Residual</t>
+        </is>
+      </c>
+      <c r="C45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>M-020</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Dureza_Total</t>
+        </is>
+      </c>
+      <c r="C46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>M-020</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Metales_Pesados</t>
+        </is>
+      </c>
+      <c r="C47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>M-020</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Turbidez</t>
+        </is>
+      </c>
+      <c r="C48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>M-021</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Cloro_Residual</t>
+        </is>
+      </c>
+      <c r="C49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>M-021</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Conductividad</t>
+        </is>
+      </c>
+      <c r="C50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>M-021</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Dureza_Total</t>
+        </is>
+      </c>
+      <c r="C51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>M-021</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Plaguicidas</t>
+        </is>
+      </c>
+      <c r="C52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>M-023</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Dureza_Total</t>
+        </is>
+      </c>
+      <c r="C53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>M-023</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Microbiologia</t>
+        </is>
+      </c>
+      <c r="C54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>M-023</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Nitratos</t>
+        </is>
+      </c>
+      <c r="C55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>M-023</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Solidos_Disueltos</t>
+        </is>
+      </c>
+      <c r="C56" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>M-024</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Cloro_Residual</t>
+        </is>
+      </c>
+      <c r="C57" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>M-024</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Microbiologia</t>
+        </is>
+      </c>
+      <c r="C58" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>M-024</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Nitratos</t>
+        </is>
+      </c>
+      <c r="C59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>M-026</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Dureza_Total</t>
+        </is>
+      </c>
+      <c r="C60" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>M-026</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Metales_Pesados</t>
+        </is>
+      </c>
+      <c r="C61" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>M-026</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Microbiologia</t>
+        </is>
+      </c>
+      <c r="C62" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>M-029</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Dureza_Total</t>
+        </is>
+      </c>
+      <c r="C63" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>M-029</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Metales_Pesados</t>
+        </is>
+      </c>
+      <c r="C64" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>M-029</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Solidos_Disueltos</t>
+        </is>
+      </c>
+      <c r="C65" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>M-029</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Turbidez</t>
+        </is>
+      </c>
+      <c r="C66" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>M-030</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Microbiologia</t>
+        </is>
+      </c>
+      <c r="C67" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>M-030</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Nitratos</t>
+        </is>
+      </c>
+      <c r="C68" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>M-030</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Solidos_Disueltos</t>
+        </is>
+      </c>
+      <c r="C69" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>M-030</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Turbidez</t>
+        </is>
+      </c>
+      <c r="C70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>M-030</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="C71" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>M-031</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Cloro_Residual</t>
+        </is>
+      </c>
+      <c r="C72" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>M-031</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Microbiologia</t>
+        </is>
+      </c>
+      <c r="C73" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>M-031</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Nitratos</t>
+        </is>
+      </c>
+      <c r="C74" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>M-031</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Plaguicidas</t>
+        </is>
+      </c>
+      <c r="C75" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>M-033</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Cloro_Residual</t>
+        </is>
+      </c>
+      <c r="C76" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>M-033</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Metales_Pesados</t>
+        </is>
+      </c>
+      <c r="C77" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>M-033</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Microbiologia</t>
+        </is>
+      </c>
+      <c r="C78" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>M-033</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="C79" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>M-034</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Plaguicidas</t>
+        </is>
+      </c>
+      <c r="C80" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>M-034</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Solidos_Disueltos</t>
+        </is>
+      </c>
+      <c r="C81" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>M-034</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Turbidez</t>
+        </is>
+      </c>
+      <c r="C82" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>M-034</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="C83" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>M-035</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Cloro_Residual</t>
+        </is>
+      </c>
+      <c r="C84" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>M-035</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Metales_Pesados</t>
+        </is>
+      </c>
+      <c r="C85" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>M-037</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Cloro_Residual</t>
+        </is>
+      </c>
+      <c r="C86" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>M-037</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Microbiologia</t>
+        </is>
+      </c>
+      <c r="C87" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>M-037</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Nitratos</t>
+        </is>
+      </c>
+      <c r="C88" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>M-041</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Conductividad</t>
+        </is>
+      </c>
+      <c r="C89" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>M-041</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="C90" t="b">
         <v>1</v>
       </c>
     </row>
